--- a/artfynd/A 36261-2026 artfynd.xlsx
+++ b/artfynd/A 36261-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136042737</v>
       </c>
       <c r="B3" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36261-2026 artfynd.xlsx
+++ b/artfynd/A 36261-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136042737</v>
       </c>
       <c r="B3" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36261-2026 artfynd.xlsx
+++ b/artfynd/A 36261-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136042737</v>
       </c>
       <c r="B3" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36261-2026 artfynd.xlsx
+++ b/artfynd/A 36261-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136042737</v>
       </c>
       <c r="B3" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36261-2026 artfynd.xlsx
+++ b/artfynd/A 36261-2026 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136042737</v>
       </c>
       <c r="B3" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
